--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="11950" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>name</t>
   </si>
@@ -120,6 +120,42 @@
   </si>
   <si>
     <t>印加寻宝</t>
+  </si>
+  <si>
+    <t>飞蛾族类</t>
+  </si>
+  <si>
+    <t>德国心脏病</t>
+  </si>
+  <si>
+    <t>犯人在跳舞</t>
+  </si>
+  <si>
+    <t>还玩好游戏</t>
+  </si>
+  <si>
+    <t>三国杀：诸侯讨董</t>
+  </si>
+  <si>
+    <t>三国杀王者之战</t>
+  </si>
+  <si>
+    <t>猩猩相惜</t>
+  </si>
+  <si>
+    <t>瞎掰王</t>
+  </si>
+  <si>
+    <t>德国蟑螂</t>
+  </si>
+  <si>
+    <t>赌命大赛</t>
+  </si>
+  <si>
+    <t>Leet Poker</t>
+  </si>
+  <si>
+    <t>小黑屋：第三版</t>
   </si>
 </sst>
 </file>
@@ -1272,7 +1308,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1372,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1793,6 +1829,246 @@
       </c>
       <c r="F26">
         <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27">
+        <v>11.7</v>
+      </c>
+      <c r="C27">
+        <v>11.7</v>
+      </c>
+      <c r="D27">
+        <v>3.5</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28">
+        <v>17.1</v>
+      </c>
+      <c r="C28">
+        <v>12.9</v>
+      </c>
+      <c r="D28">
+        <v>5.9</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29">
+        <v>14.1</v>
+      </c>
+      <c r="C29">
+        <v>13.1</v>
+      </c>
+      <c r="D29">
+        <v>3.1</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30">
+        <v>15.2</v>
+      </c>
+      <c r="C30">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31">
+        <v>20</v>
+      </c>
+      <c r="C31">
+        <v>15.2</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32">
+        <v>13</v>
+      </c>
+      <c r="C32">
+        <v>9</v>
+      </c>
+      <c r="D32">
+        <v>3.5</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <v>10</v>
+      </c>
+      <c r="D33">
+        <v>5.1</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34">
+        <v>14.9</v>
+      </c>
+      <c r="C34">
+        <v>9.8</v>
+      </c>
+      <c r="D34">
+        <v>5.2</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35">
+        <v>11.3</v>
+      </c>
+      <c r="C35">
+        <v>11.3</v>
+      </c>
+      <c r="D35">
+        <v>3.5</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36">
+        <v>15.3</v>
+      </c>
+      <c r="C36">
+        <v>15.3</v>
+      </c>
+      <c r="D36">
+        <v>7</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37">
+        <v>12</v>
+      </c>
+      <c r="C37">
+        <v>9.2</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38">
+        <v>26.8</v>
+      </c>
+      <c r="C38">
+        <v>26.8</v>
+      </c>
+      <c r="D38">
+        <v>8.8</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
